--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24795" windowHeight="7470"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>客户编码</t>
   </si>
@@ -22,6 +35,9 @@
     <t>客户名称</t>
   </si>
   <si>
+    <t>国家</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -41,6 +57,9 @@
   </si>
   <si>
     <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.countryName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -61,7 +80,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -72,21 +91,21 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -94,7 +113,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -102,14 +121,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -117,7 +136,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -125,7 +144,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -133,7 +152,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -141,7 +160,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -149,14 +168,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -164,7 +183,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +191,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -180,14 +199,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -195,42 +214,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -712,55 +731,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1029,17 +1048,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="23.6285714285714" customWidth="1"/>
-    <col min="2" max="2" width="35.6285714285714" customWidth="1"/>
-    <col min="3" max="3" width="20.6285714285714" customWidth="1"/>
-    <col min="4" max="4" width="22.3714285714286" customWidth="1"/>
-    <col min="5" max="7" width="20.6285714285714" customWidth="1"/>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="2" max="3" width="35.625" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="22.375" customWidth="1"/>
+    <col min="6" max="8" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,32 +1080,38 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
-      <c r="C3" s="2"/>
+    <row r="3" spans="4:4">
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -4,30 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24795" windowHeight="7470"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>客户编码</t>
   </si>
@@ -35,9 +22,6 @@
     <t>客户名称</t>
   </si>
   <si>
-    <t>国家</t>
-  </si>
-  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -57,9 +41,6 @@
   </si>
   <si>
     <t>{.name}</t>
-  </si>
-  <si>
-    <t>{.countryName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -80,7 +61,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -91,21 +72,21 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -113,7 +94,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -121,14 +102,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -136,7 +117,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -144,7 +125,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -152,7 +133,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -160,7 +141,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -168,14 +149,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -183,7 +164,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -191,7 +172,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -199,14 +180,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -214,42 +195,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -731,55 +712,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1048,17 +1029,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="23.625" customWidth="1"/>
-    <col min="2" max="3" width="35.625" customWidth="1"/>
-    <col min="4" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="8" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="23.6285714285714" customWidth="1"/>
+    <col min="2" max="2" width="35.6285714285714" customWidth="1"/>
+    <col min="3" max="3" width="20.6285714285714" customWidth="1"/>
+    <col min="4" max="4" width="22.3714285714286" customWidth="1"/>
+    <col min="5" max="7" width="20.6285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,38 +1061,32 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="4:4">
-      <c r="D3" s="2"/>
+    <row r="3" spans="3:3">
+      <c r="C3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24795" windowHeight="7470"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>客户编码</t>
   </si>
@@ -22,6 +35,9 @@
     <t>客户名称</t>
   </si>
   <si>
+    <t>国家</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -41,6 +57,9 @@
   </si>
   <si>
     <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.countryName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -61,7 +80,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -72,21 +91,21 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -94,7 +113,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -102,14 +121,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -117,7 +136,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -125,7 +144,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -133,7 +152,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -141,7 +160,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -149,14 +168,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -164,7 +183,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +191,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -180,14 +199,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -195,42 +214,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -712,55 +731,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1029,17 +1048,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="23.6285714285714" customWidth="1"/>
-    <col min="2" max="2" width="35.6285714285714" customWidth="1"/>
-    <col min="3" max="3" width="20.6285714285714" customWidth="1"/>
-    <col min="4" max="4" width="22.3714285714286" customWidth="1"/>
-    <col min="5" max="7" width="20.6285714285714" customWidth="1"/>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="2" max="2" width="35.625" customWidth="1"/>
+    <col min="3" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="22.375" customWidth="1"/>
+    <col min="6" max="8" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,32 +1080,39 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
+    <row r="3" spans="3:4">
       <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>客户编码</t>
   </si>
@@ -53,6 +53,18 @@
     <t>创建时间</t>
   </si>
   <si>
+    <t>结算币别</t>
+  </si>
+  <si>
+    <t>财务组织</t>
+  </si>
+  <si>
+    <t>启用时间</t>
+  </si>
+  <si>
+    <t>停用时间</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -75,6 +87,18 @@
   </si>
   <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.currencyName}</t>
+  </si>
+  <si>
+    <t>{.financialOrganizationName}</t>
+  </si>
+  <si>
+    <t>{.enableTime}</t>
+  </si>
+  <si>
+    <t>{.downTime}</t>
   </si>
 </sst>
 </file>
@@ -1048,17 +1072,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="7"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="35.625" customWidth="1"/>
     <col min="3" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="5" width="22.375" customWidth="1"/>
     <col min="6" max="8" width="20.625" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,31 +1111,55 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="3:4">

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="模板" sheetId="1" r:id="rId1"/>
+    <sheet name="客户信息" sheetId="4" r:id="rId1"/>
+    <sheet name="联系人地址信息" sheetId="2" r:id="rId2"/>
+    <sheet name="发票信息" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="85">
   <si>
     <t>客户编码</t>
   </si>
@@ -35,15 +37,51 @@
     <t>客户名称</t>
   </si>
   <si>
+    <t>简称</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
+    <t>省份</t>
+  </si>
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>销售员</t>
+  </si>
+  <si>
+    <t>平台类型</t>
+  </si>
+  <si>
+    <t>公司类别</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
     <t>启用状态</t>
   </si>
   <si>
+    <t>使用组织</t>
+  </si>
+  <si>
+    <t>客户分组</t>
+  </si>
+  <si>
+    <t>对应组织</t>
+  </si>
+  <si>
+    <t>客户属性</t>
+  </si>
+  <si>
+    <t>通讯地址</t>
+  </si>
+  <si>
     <t>最新审核人</t>
   </si>
   <si>
@@ -53,33 +91,57 @@
     <t>创建时间</t>
   </si>
   <si>
-    <t>结算币别</t>
-  </si>
-  <si>
-    <t>财务组织</t>
-  </si>
-  <si>
-    <t>启用时间</t>
-  </si>
-  <si>
-    <t>停用时间</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
     <t>{.name}</t>
   </si>
   <si>
+    <t>{.shortName}</t>
+  </si>
+  <si>
+    <t>{.areaName}</t>
+  </si>
+  <si>
     <t>{.countryName}</t>
   </si>
   <si>
+    <t>{.provinceName}</t>
+  </si>
+  <si>
+    <t>{.cityName}</t>
+  </si>
+  <si>
+    <t>{.sellerName}</t>
+  </si>
+  <si>
+    <t>{.businessModeName}</t>
+  </si>
+  <si>
+    <t>{.companyCategoryDictName}</t>
+  </si>
+  <si>
     <t>{.approveStatusName}</t>
   </si>
   <si>
     <t>{.disabledName}</t>
   </si>
   <si>
+    <t>{.useOrgName}</t>
+  </si>
+  <si>
+    <t>{.groupName}</t>
+  </si>
+  <si>
+    <t>{.innerOrgName}</t>
+  </si>
+  <si>
+    <t>{.customerProperty}</t>
+  </si>
+  <si>
+    <t>{.mailAddress}</t>
+  </si>
+  <si>
     <t>{.approveUserName}</t>
   </si>
   <si>
@@ -89,16 +151,139 @@
     <t>{.createTime}</t>
   </si>
   <si>
-    <t>{.currencyName}</t>
-  </si>
-  <si>
-    <t>{.financialOrganizationName}</t>
-  </si>
-  <si>
-    <t>{.enableTime}</t>
-  </si>
-  <si>
-    <t>{.downTime}</t>
+    <t>联系人</t>
+  </si>
+  <si>
+    <t>职务</t>
+  </si>
+  <si>
+    <t>联系人电话</t>
+  </si>
+  <si>
+    <t>联系人邮箱</t>
+  </si>
+  <si>
+    <t>是否默认联系人</t>
+  </si>
+  <si>
+    <t>联系人启用状态</t>
+  </si>
+  <si>
+    <t>联系人备注</t>
+  </si>
+  <si>
+    <t>详细地址</t>
+  </si>
+  <si>
+    <t>地址类型</t>
+  </si>
+  <si>
+    <t>收货人电话</t>
+  </si>
+  <si>
+    <t>收货人邮箱</t>
+  </si>
+  <si>
+    <t>是否默认地址</t>
+  </si>
+  <si>
+    <t>地址启用状态</t>
+  </si>
+  <si>
+    <t>地址备注</t>
+  </si>
+  <si>
+    <t>{.person}</t>
+  </si>
+  <si>
+    <t>{.position}</t>
+  </si>
+  <si>
+    <t>{.personTelNumber}</t>
+  </si>
+  <si>
+    <t>{.personEmail}</t>
+  </si>
+  <si>
+    <t>{.personDisabledName}</t>
+  </si>
+  <si>
+    <t>{.personIsDefaultName}</t>
+  </si>
+  <si>
+    <t>{.personRemark}</t>
+  </si>
+  <si>
+    <t>{.address}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.addressTelNumber}</t>
+  </si>
+  <si>
+    <t>{.addressEmail}</t>
+  </si>
+  <si>
+    <t>{.addressIsDefaultName}</t>
+  </si>
+  <si>
+    <t>{.addressDisabledName}</t>
+  </si>
+  <si>
+    <t>{.addressRemark}</t>
+  </si>
+  <si>
+    <t>发票抬头</t>
+  </si>
+  <si>
+    <t>发票类型</t>
+  </si>
+  <si>
+    <t>开户银行</t>
+  </si>
+  <si>
+    <t>银行账号</t>
+  </si>
+  <si>
+    <t>纳税登记号</t>
+  </si>
+  <si>
+    <t>开票联系电话</t>
+  </si>
+  <si>
+    <t>开票通讯地址</t>
+  </si>
+  <si>
+    <t>是否默认</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>{.head}</t>
+  </si>
+  <si>
+    <t>{.bankName}</t>
+  </si>
+  <si>
+    <t>{.bankAccount}</t>
+  </si>
+  <si>
+    <t>{.taxRegisterCode}</t>
+  </si>
+  <si>
+    <t>{.invoiceTel}</t>
+  </si>
+  <si>
+    <t>{.invoiceAddress}</t>
+  </si>
+  <si>
+    <t>{.isDefaultName}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
 </sst>
 </file>
@@ -111,9 +296,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -472,12 +664,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -598,159 +805,162 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1072,31 +1282,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
-    <col min="2" max="2" width="35.625" customWidth="1"/>
-    <col min="3" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="8" width="20.625" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="7" width="20.625" customWidth="1"/>
+    <col min="8" max="8" width="17.875" customWidth="1"/>
+    <col min="9" max="9" width="27.625" customWidth="1"/>
+    <col min="10" max="10" width="26.875" customWidth="1"/>
+    <col min="11" max="11" width="19.875" customWidth="1"/>
+    <col min="12" max="12" width="15.75" customWidth="1"/>
+    <col min="13" max="13" width="15.625" customWidth="1"/>
+    <col min="14" max="14" width="16.25" customWidth="1"/>
+    <col min="15" max="15" width="16.625" customWidth="1"/>
+    <col min="16" max="16" width="22.25" customWidth="1"/>
+    <col min="17" max="17" width="17.25" customWidth="1"/>
+    <col min="18" max="18" width="18.25" customWidth="1"/>
+    <col min="19" max="19" width="16.625" customWidth="1"/>
+    <col min="20" max="20" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="14.25" spans="1:20">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1123,51 +1342,311 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="1" t="s">
+    <row r="2" spans="1:20">
+      <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="3:4">
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="10" width="14.375" customWidth="1"/>
+    <col min="12" max="12" width="13.875" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="15.875" customWidth="1"/>
+    <col min="16" max="16" width="18.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.75" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.75" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>客户编码</t>
   </si>
@@ -35,6 +35,9 @@
     <t>客户名称</t>
   </si>
   <si>
+    <t>军区</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
   </si>
   <si>
     <t>{.countryName}</t>
@@ -1072,21 +1078,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="35.625" customWidth="1"/>
-    <col min="3" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="8" width="20.625" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="13.125" customWidth="1"/>
+    <col min="3" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="22.375" customWidth="1"/>
+    <col min="7" max="9" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="17.875" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1123,48 +1129,55 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="3:4">
+    <row r="3" spans="3:5">
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -205,10 +205,10 @@
     <t>{.personEmail}</t>
   </si>
   <si>
+    <t>{.personIsDefaultName}</t>
+  </si>
+  <si>
     <t>{.personDisabledName}</t>
-  </si>
-  <si>
-    <t>{.personIsDefaultName}</t>
   </si>
   <si>
     <t>{.personRemark}</t>
@@ -1454,7 +1454,7 @@
     <col min="16" max="16" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.75" spans="1:16">
+    <row r="1" ht="14.25" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1575,7 +1575,7 @@
     <col min="10" max="10" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.75" spans="1:11">
+    <row r="1" ht="14.25" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -7,7 +7,9 @@
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="模板" sheetId="1" r:id="rId1"/>
+    <sheet name="客户信息" sheetId="4" r:id="rId1"/>
+    <sheet name="联系人地址信息" sheetId="2" r:id="rId2"/>
+    <sheet name="发票信息" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
   <si>
     <t>客户编码</t>
   </si>
@@ -35,18 +37,54 @@
     <t>客户名称</t>
   </si>
   <si>
+    <t>简称</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
     <t>军区</t>
   </si>
   <si>
     <t>国家</t>
   </si>
   <si>
+    <t>省份</t>
+  </si>
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>销售员</t>
+  </si>
+  <si>
+    <t>平台类型</t>
+  </si>
+  <si>
+    <t>公司类别</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
     <t>启用状态</t>
   </si>
   <si>
+    <t>使用组织</t>
+  </si>
+  <si>
+    <t>客户分组</t>
+  </si>
+  <si>
+    <t>对应组织</t>
+  </si>
+  <si>
+    <t>客户属性</t>
+  </si>
+  <si>
+    <t>通讯地址</t>
+  </si>
+  <si>
     <t>最新审核人</t>
   </si>
   <si>
@@ -56,36 +94,60 @@
     <t>创建时间</t>
   </si>
   <si>
-    <t>结算币别</t>
-  </si>
-  <si>
-    <t>财务组织</t>
-  </si>
-  <si>
-    <t>启用时间</t>
-  </si>
-  <si>
-    <t>停用时间</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
     <t>{.name}</t>
   </si>
   <si>
+    <t>{.shortName}</t>
+  </si>
+  <si>
+    <t>{.areaName}</t>
+  </si>
+  <si>
     <t>{.partitionName}</t>
   </si>
   <si>
     <t>{.countryName}</t>
   </si>
   <si>
+    <t>{.provinceName}</t>
+  </si>
+  <si>
+    <t>{.cityName}</t>
+  </si>
+  <si>
+    <t>{.sellerName}</t>
+  </si>
+  <si>
+    <t>{.businessModeName}</t>
+  </si>
+  <si>
+    <t>{.companyCategoryDictName}</t>
+  </si>
+  <si>
     <t>{.approveStatusName}</t>
   </si>
   <si>
     <t>{.disabledName}</t>
   </si>
   <si>
+    <t>{.useOrgName}</t>
+  </si>
+  <si>
+    <t>{.groupName}</t>
+  </si>
+  <si>
+    <t>{.innerOrgName}</t>
+  </si>
+  <si>
+    <t>{.customerProperty}</t>
+  </si>
+  <si>
+    <t>{.mailAddress}</t>
+  </si>
+  <si>
     <t>{.approveUserName}</t>
   </si>
   <si>
@@ -95,16 +157,139 @@
     <t>{.createTime}</t>
   </si>
   <si>
-    <t>{.currencyName}</t>
-  </si>
-  <si>
-    <t>{.financialOrganizationName}</t>
-  </si>
-  <si>
-    <t>{.enableTime}</t>
-  </si>
-  <si>
-    <t>{.downTime}</t>
+    <t>联系人</t>
+  </si>
+  <si>
+    <t>职务</t>
+  </si>
+  <si>
+    <t>联系人电话</t>
+  </si>
+  <si>
+    <t>联系人邮箱</t>
+  </si>
+  <si>
+    <t>是否默认联系人</t>
+  </si>
+  <si>
+    <t>联系人启用状态</t>
+  </si>
+  <si>
+    <t>联系人备注</t>
+  </si>
+  <si>
+    <t>详细地址</t>
+  </si>
+  <si>
+    <t>地址类型</t>
+  </si>
+  <si>
+    <t>收货人电话</t>
+  </si>
+  <si>
+    <t>收货人邮箱</t>
+  </si>
+  <si>
+    <t>是否默认地址</t>
+  </si>
+  <si>
+    <t>地址启用状态</t>
+  </si>
+  <si>
+    <t>地址备注</t>
+  </si>
+  <si>
+    <t>{.person}</t>
+  </si>
+  <si>
+    <t>{.position}</t>
+  </si>
+  <si>
+    <t>{.personTelNumber}</t>
+  </si>
+  <si>
+    <t>{.personEmail}</t>
+  </si>
+  <si>
+    <t>{.personIsDefaultName}</t>
+  </si>
+  <si>
+    <t>{.personDisabledName}</t>
+  </si>
+  <si>
+    <t>{.personRemark}</t>
+  </si>
+  <si>
+    <t>{.address}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.addressTelNumber}</t>
+  </si>
+  <si>
+    <t>{.addressEmail}</t>
+  </si>
+  <si>
+    <t>{.addressIsDefaultName}</t>
+  </si>
+  <si>
+    <t>{.addressDisabledName}</t>
+  </si>
+  <si>
+    <t>{.addressRemark}</t>
+  </si>
+  <si>
+    <t>发票抬头</t>
+  </si>
+  <si>
+    <t>发票类型</t>
+  </si>
+  <si>
+    <t>开户银行</t>
+  </si>
+  <si>
+    <t>银行账号</t>
+  </si>
+  <si>
+    <t>纳税登记号</t>
+  </si>
+  <si>
+    <t>开票联系电话</t>
+  </si>
+  <si>
+    <t>开票通讯地址</t>
+  </si>
+  <si>
+    <t>是否默认</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>{.head}</t>
+  </si>
+  <si>
+    <t>{.bankName}</t>
+  </si>
+  <si>
+    <t>{.bankAccount}</t>
+  </si>
+  <si>
+    <t>{.taxRegisterCode}</t>
+  </si>
+  <si>
+    <t>{.invoiceTel}</t>
+  </si>
+  <si>
+    <t>{.invoiceAddress}</t>
+  </si>
+  <si>
+    <t>{.isDefaultName}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
 </sst>
 </file>
@@ -117,9 +302,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -478,12 +670,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -604,159 +811,162 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1078,34 +1288,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
-    <col min="2" max="2" width="35.625" customWidth="1"/>
-    <col min="3" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="22.375" customWidth="1"/>
-    <col min="7" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="17.875" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="8" width="20.625" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="27.625" customWidth="1"/>
+    <col min="11" max="11" width="26.875" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="13" max="13" width="15.75" customWidth="1"/>
+    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="15" max="15" width="16.25" customWidth="1"/>
+    <col min="16" max="16" width="16.625" customWidth="1"/>
+    <col min="17" max="17" width="22.25" customWidth="1"/>
+    <col min="18" max="18" width="17.25" customWidth="1"/>
+    <col min="19" max="19" width="18.25" customWidth="1"/>
+    <col min="20" max="20" width="16.625" customWidth="1"/>
+    <col min="21" max="21" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="14.25" spans="1:21">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1132,55 +1351,314 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
+    <row r="2" spans="1:21">
+      <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="3:5">
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="10" width="14.375" customWidth="1"/>
+    <col min="12" max="12" width="13.875" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="15.875" customWidth="1"/>
+    <col min="16" max="16" width="18.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="客户信息" sheetId="4" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
   <si>
     <t>客户编码</t>
   </si>
@@ -43,6 +43,9 @@
     <t>区域</t>
   </si>
   <si>
+    <t>军区</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>{.areaName}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
   </si>
   <si>
     <t>{.countryName}</t>
@@ -1282,30 +1288,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="16.125" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="7" width="20.625" customWidth="1"/>
-    <col min="8" max="8" width="17.875" customWidth="1"/>
-    <col min="9" max="9" width="27.625" customWidth="1"/>
-    <col min="10" max="10" width="26.875" customWidth="1"/>
-    <col min="11" max="11" width="19.875" customWidth="1"/>
-    <col min="12" max="12" width="15.75" customWidth="1"/>
-    <col min="13" max="13" width="15.625" customWidth="1"/>
-    <col min="14" max="14" width="16.25" customWidth="1"/>
-    <col min="15" max="15" width="16.625" customWidth="1"/>
-    <col min="16" max="16" width="22.25" customWidth="1"/>
-    <col min="17" max="17" width="17.25" customWidth="1"/>
-    <col min="18" max="18" width="18.25" customWidth="1"/>
-    <col min="19" max="19" width="16.625" customWidth="1"/>
-    <col min="20" max="20" width="14.25" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="8" width="20.625" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="27.625" customWidth="1"/>
+    <col min="11" max="11" width="26.875" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="13" max="13" width="15.75" customWidth="1"/>
+    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="15" max="15" width="16.25" customWidth="1"/>
+    <col min="16" max="16" width="16.625" customWidth="1"/>
+    <col min="17" max="17" width="22.25" customWidth="1"/>
+    <col min="18" max="18" width="17.25" customWidth="1"/>
+    <col min="19" max="19" width="18.25" customWidth="1"/>
+    <col min="20" max="20" width="16.625" customWidth="1"/>
+    <col min="21" max="21" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:20">
+    <row r="1" ht="14.25" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1324,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1366,67 +1372,73 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1462,96 +1474,96 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1583,66 +1595,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -670,27 +670,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -832,7 +817,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -844,34 +829,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -963,10 +948,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1311,7 +1296,7 @@
     <col min="21" max="21" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:21">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1466,7 +1451,7 @@
     <col min="16" max="16" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:16">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1587,7 +1572,7 @@
     <col min="10" max="10" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
   <si>
     <t>客户编码</t>
   </si>
@@ -55,6 +55,9 @@
     <t>城市</t>
   </si>
   <si>
+    <t>销售部门</t>
+  </si>
+  <si>
     <t>销售员</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
   </si>
   <si>
     <t>{.cityName}</t>
+  </si>
+  <si>
+    <t>{.salesDeptName}</t>
   </si>
   <si>
     <t>{.sellerName}</t>
@@ -1273,30 +1279,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="16.125" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="8" width="20.625" customWidth="1"/>
-    <col min="9" max="9" width="17.875" customWidth="1"/>
-    <col min="10" max="10" width="27.625" customWidth="1"/>
-    <col min="11" max="11" width="26.875" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="15.75" customWidth="1"/>
-    <col min="14" max="14" width="15.625" customWidth="1"/>
-    <col min="15" max="15" width="16.25" customWidth="1"/>
-    <col min="16" max="16" width="16.625" customWidth="1"/>
-    <col min="17" max="17" width="22.25" customWidth="1"/>
-    <col min="18" max="18" width="17.25" customWidth="1"/>
-    <col min="19" max="19" width="18.25" customWidth="1"/>
-    <col min="20" max="20" width="16.625" customWidth="1"/>
-    <col min="21" max="21" width="14.25" customWidth="1"/>
+    <col min="6" max="9" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+    <col min="11" max="11" width="27.625" customWidth="1"/>
+    <col min="12" max="12" width="26.875" customWidth="1"/>
+    <col min="13" max="13" width="19.875" customWidth="1"/>
+    <col min="14" max="14" width="15.75" customWidth="1"/>
+    <col min="15" max="15" width="15.625" customWidth="1"/>
+    <col min="16" max="16" width="16.25" customWidth="1"/>
+    <col min="17" max="17" width="16.625" customWidth="1"/>
+    <col min="18" max="18" width="22.25" customWidth="1"/>
+    <col min="19" max="19" width="17.25" customWidth="1"/>
+    <col min="20" max="20" width="18.25" customWidth="1"/>
+    <col min="21" max="21" width="16.625" customWidth="1"/>
+    <col min="22" max="22" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1360,70 +1366,76 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1459,96 +1471,96 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1580,66 +1592,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/CustomerExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="91">
   <si>
     <t>客户编码</t>
   </si>
@@ -61,6 +61,9 @@
     <t>销售员</t>
   </si>
   <si>
+    <t>平台归属</t>
+  </si>
+  <si>
     <t>平台类型</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
   </si>
   <si>
     <t>{.sellerName}</t>
+  </si>
+  <si>
+    <t>{.platformTypeName}</t>
   </si>
   <si>
     <t>{.businessModeName}</t>
@@ -1279,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -1288,21 +1294,21 @@
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="9" width="20.625" customWidth="1"/>
     <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="27.625" customWidth="1"/>
-    <col min="12" max="12" width="26.875" customWidth="1"/>
-    <col min="13" max="13" width="19.875" customWidth="1"/>
-    <col min="14" max="14" width="15.75" customWidth="1"/>
-    <col min="15" max="15" width="15.625" customWidth="1"/>
-    <col min="16" max="16" width="16.25" customWidth="1"/>
-    <col min="17" max="17" width="16.625" customWidth="1"/>
-    <col min="18" max="18" width="22.25" customWidth="1"/>
-    <col min="19" max="19" width="17.25" customWidth="1"/>
-    <col min="20" max="20" width="18.25" customWidth="1"/>
-    <col min="21" max="21" width="16.625" customWidth="1"/>
-    <col min="22" max="22" width="14.25" customWidth="1"/>
+    <col min="11" max="12" width="27.625" customWidth="1"/>
+    <col min="13" max="13" width="26.875" customWidth="1"/>
+    <col min="14" max="14" width="19.875" customWidth="1"/>
+    <col min="15" max="15" width="15.75" customWidth="1"/>
+    <col min="16" max="16" width="15.625" customWidth="1"/>
+    <col min="17" max="17" width="16.25" customWidth="1"/>
+    <col min="18" max="18" width="16.625" customWidth="1"/>
+    <col min="19" max="19" width="22.25" customWidth="1"/>
+    <col min="20" max="20" width="17.25" customWidth="1"/>
+    <col min="21" max="21" width="18.25" customWidth="1"/>
+    <col min="22" max="22" width="16.625" customWidth="1"/>
+    <col min="23" max="23" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1369,73 +1375,79 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1471,96 +1483,96 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1592,66 +1604,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
